--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486336_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486336_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5366</v>
+        <v>7.5734</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3476</v>
+        <v>7.2611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.189</v>
+        <v>0.3123</v>
       </c>
       <c r="G2" t="n">
         <v>5.6087</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3973</v>
+        <v>-0.3605</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2704</v>
+        <v>-0.3569</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1269</v>
+        <v>-0.0036</v>
       </c>
       <c r="V2" t="n">
         <v>1.8902</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3393</v>
+        <v>5.9878</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6535</v>
+        <v>2.6102</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6858</v>
+        <v>3.3776</v>
       </c>
       <c r="G3" t="n">
         <v>3.3601</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3906</v>
+        <v>-0.742</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2584</v>
+        <v>-0.3016</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1322</v>
+        <v>-0.4404</v>
       </c>
       <c r="V3" t="n">
         <v>2.0647</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6275</v>
+        <v>5.2297</v>
       </c>
       <c r="E4" t="n">
-        <v>3.715</v>
+        <v>3.2247</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9125</v>
+        <v>2.0049</v>
       </c>
       <c r="G4" t="n">
         <v>2.7142</v>
@@ -766,13 +766,13 @@
         <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3032</v>
+        <v>-0.0946</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4062</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.103</v>
+        <v>-0.0105</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2319</v>
+        <v>2.9517</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0577</v>
+        <v>0.4557</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1742</v>
+        <v>2.496</v>
       </c>
       <c r="G5" t="n">
         <v>-2.2527</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8119</v>
+        <v>0.5317</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2692</v>
+        <v>-0.3329</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5427</v>
+        <v>0.8646</v>
       </c>
       <c r="V5" t="n">
         <v>3.5851</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9005</v>
+        <v>1.9151</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3407</v>
+        <v>0.6327</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5598</v>
+        <v>1.2824</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9965000000000001</v>
@@ -922,13 +922,13 @@
         <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4505</v>
+        <v>-0.4359</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.4494</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2909</v>
+        <v>0.0135</v>
       </c>
       <c r="V6" t="n">
         <v>2.2599</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9882</v>
+        <v>1.416</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6785</v>
+        <v>1.0138</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3097</v>
+        <v>0.4022</v>
       </c>
       <c r="G7" t="n">
         <v>1.4301</v>
@@ -1000,13 +1000,13 @@
         <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3119</v>
+        <v>-0.8841</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.3377</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6389</v>
+        <v>-0.5465</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0282</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0191</v>
+        <v>0.6896</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0473</v>
+        <v>0.2918</v>
       </c>
       <c r="G8" t="n">
         <v>0.2677</v>
@@ -1078,13 +1078,13 @@
         <v>2.6101</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.776</v>
+        <v>-0.7664</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0034</v>
+        <v>-0.3329</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7726</v>
+        <v>-0.4335</v>
       </c>
       <c r="V8" t="n">
         <v>-1.13</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.895</v>
+        <v>-0.7957</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.882</v>
+        <v>-0.8136</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0129</v>
+        <v>0.0179</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6294999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2655</v>
+        <v>-0.1661</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.137</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3826</v>
+        <v>-1.2216</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1014</v>
+        <v>-2.0329</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7188</v>
+        <v>0.8112</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2012</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4419</v>
+        <v>-0.2809</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.548</v>
+        <v>-0.4795</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1061</v>
+        <v>0.1986</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1745</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.124</v>
+        <v>-1.2579</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7385</v>
+        <v>-1.3348</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3855</v>
+        <v>0.0769</v>
       </c>
       <c r="G11" t="n">
         <v>0.2815</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1662</v>
+        <v>-0.3001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8784</v>
+        <v>-0.4747</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2878</v>
+        <v>0.1745</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6743</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5899</v>
+        <v>-2.4906</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.882</v>
+        <v>-0.8136</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7079</v>
+        <v>-1.6771</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6294999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2655</v>
+        <v>-0.1661</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.137</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.695</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.6043</v>
+        <v>20.2893</v>
       </c>
       <c r="E13" t="n">
-        <v>10.2082</v>
+        <v>10.8929</v>
       </c>
       <c r="F13" t="n">
-        <v>9.3962</v>
+        <v>9.396099999999999</v>
       </c>
       <c r="G13" t="n">
         <v>7.952899999999998</v>
@@ -1468,13 +1468,13 @@
         <v>17.4006</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.3503</v>
+        <v>-3.665</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.9715</v>
+        <v>-3.2867</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3787</v>
+        <v>-0.3784999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>5.126100000000002</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3389</v>
+        <v>1.3468</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0191</v>
+        <v>-0.3683</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3198</v>
+        <v>1.7151</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0224</v>
+        <v>-0.4506</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5117</v>
+        <v>0.6873</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4893</v>
+        <v>-1.1379</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4879</v>
+        <v>-0.7564</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1492</v>
+        <v>0.4261</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3387</v>
+        <v>-1.1825</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.5103</v>
+        <v>0.3058</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6608</v>
+        <v>0.2612</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8495</v>
+        <v>0.0446</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7522</v>
+        <v>1.1449</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8362</v>
+        <v>0.3882</v>
       </c>
       <c r="U14" t="n">
-        <v>0.916</v>
+        <v>0.7568</v>
       </c>
       <c r="V14" t="n">
-        <v>1.479</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4432</v>
+        <v>1.3089</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0483</v>
+        <v>1.1715</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6052</v>
+        <v>0.1374</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7475</v>
+        <v>1.3678</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4757</v>
+        <v>0.4196</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2717</v>
+        <v>0.9483</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8528</v>
+        <v>2.6055</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4121</v>
+        <v>0.7879</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4407</v>
+        <v>1.8177</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1053</v>
+        <v>-1.2377</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0636</v>
+        <v>-0.3683</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1689</v>
+        <v>-0.8694</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.87</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>-3.4801</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6305</v>
+        <v>0.2689</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0227</v>
+        <v>-0.2139</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6078</v>
+        <v>0.4828</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.0647</v>
+        <v>2.0647</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7395</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3756</v>
+        <v>1.0835</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1715</v>
+        <v>1.6013</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2041</v>
+        <v>-0.5178</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3678</v>
+        <v>2.7475</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4196</v>
+        <v>2.4757</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9483</v>
+        <v>0.2717</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6055</v>
+        <v>2.8528</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7879</v>
+        <v>2.4121</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8177</v>
+        <v>0.4407</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2377</v>
+        <v>-0.1053</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3683</v>
+        <v>0.0636</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8694</v>
+        <v>-0.1689</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.3926</v>
+        <v>-0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4801</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3356</v>
+        <v>1.2708</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2139</v>
+        <v>0.5756</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5495</v>
+        <v>0.6952</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0647</v>
+        <v>-2.0647</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>-0.7395</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3648</v>
+        <v>1.0698</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1448</v>
+        <v>1.125</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5096</v>
+        <v>-0.0552</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4506</v>
+        <v>-1.0224</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6873</v>
+        <v>-1.5117</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1379</v>
+        <v>0.4893</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7564</v>
+        <v>1.4879</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4261</v>
+        <v>0.1492</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1825</v>
+        <v>1.3387</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3058</v>
+        <v>-2.5103</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2612</v>
+        <v>-1.6608</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0446</v>
+        <v>-0.8495</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1629</v>
+        <v>1.4832</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6117</v>
+        <v>0.9421</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5512</v>
+        <v>0.5411</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.479</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.479</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8721</v>
+        <v>-0.4752</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8386</v>
+        <v>1.1739</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7107</v>
+        <v>-1.6491</v>
       </c>
       <c r="G18" t="n">
         <v>0.8193</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0394</v>
+        <v>0.3575</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3425</v>
+        <v>-0.0072</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3031</v>
+        <v>0.3647</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8695</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1603</v>
+        <v>-1.0485</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7953</v>
+        <v>-0.6835</v>
       </c>
       <c r="F19" t="n">
         <v>-0.365</v>
@@ -1936,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5954</v>
+        <v>-1.6763</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9061</v>
+        <v>-1.0179</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6893</v>
+        <v>-0.6584</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7345</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6166</v>
+        <v>0.5357</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1202</v>
       </c>
       <c r="U20" t="n">
-        <v>0.625</v>
+        <v>0.6558</v>
       </c>
       <c r="V20" t="n">
         <v>-1.13</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. KELLY</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3642</v>
+        <v>-1.6796</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0134</v>
+        <v>0.1881</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3507</v>
+        <v>-1.8678</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0829</v>
+        <v>-1.5709</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2846</v>
+        <v>-0.4777</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2017</v>
+        <v>-1.0933</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3261</v>
+        <v>0.5074</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9564</v>
+        <v>0.6022</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6303</v>
+        <v>-0.0948</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2432</v>
+        <v>-2.0783</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3282</v>
+        <v>-1.0799</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5714</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="P21" t="n">
         <v>-1.305</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4916</v>
+        <v>0.0664</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1644</v>
+        <v>-0.1442</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6728</v>
+        <v>0.2106</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.6504</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3797</v>
+        <v>-1.8442</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1471</v>
+        <v>-2.4142</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2325</v>
+        <v>0.57</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5709</v>
+        <v>-3.0734</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4777</v>
+        <v>-0.6024</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0933</v>
+        <v>-2.471</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5074</v>
+        <v>-2.4158</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6022</v>
+        <v>-0.4316</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0948</v>
+        <v>-1.9841</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0783</v>
+        <v>-0.6576</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0799</v>
+        <v>-0.1707</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.4869</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.305</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6337</v>
+        <v>0.9677</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4795</v>
+        <v>0.1767</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1542</v>
+        <v>0.791</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>0.9141</v>
       </c>
       <c r="W22" t="n">
         <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2159</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>A. KELLY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7793</v>
+        <v>-1.9107</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8612</v>
+        <v>-0.6781</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0819</v>
+        <v>-1.2325</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0734</v>
+        <v>2.0829</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6024</v>
+        <v>3.2846</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.471</v>
+        <v>-1.2017</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4158</v>
+        <v>2.3261</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4316</v>
+        <v>2.9564</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9841</v>
+        <v>-0.6303</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6576</v>
+        <v>-0.2432</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1707</v>
+        <v>0.3282</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4869</v>
+        <v>-0.5714</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0326</v>
+        <v>-0.0382</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2704</v>
+        <v>-0.8292</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3029</v>
+        <v>0.791</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9141</v>
+        <v>-2.6504</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2159</v>
+        <v>-2.6504</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.032</v>
+        <v>-2.9832</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8658</v>
+        <v>-2.0894</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1661</v>
+        <v>-0.8938</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9599</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0377</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1406</v>
+        <v>-0.0829</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1029</v>
+        <v>0.1694</v>
       </c>
       <c r="V24" t="n">
         <v>0.1952</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.9438</v>
+        <v>-11.3054</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7398</v>
+        <v>-7.4045</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.204</v>
+        <v>-3.9009</v>
       </c>
       <c r="G25" t="n">
         <v>-4.0667</v>
@@ -2404,13 +2404,13 @@
         <v>0.87</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9848</v>
+        <v>-0.3464</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.3497</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2998</v>
+        <v>0.0033</v>
       </c>
       <c r="V25" t="n">
         <v>-3.1947</v>
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-19.6043</v>
+        <v>-18.1141</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.396000000000001</v>
+        <v>-9.396100000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.2081</v>
+        <v>-8.718</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.9527</v>
+        <v>-7.952699999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5023000000000009</v>
+        <v>-0.5023</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.4506</v>
+        <v>-7.450599999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>2.499699999999999</v>
+        <v>2.4997</v>
       </c>
       <c r="K26" t="n">
-        <v>2.846200000000001</v>
+        <v>2.8462</v>
       </c>
       <c r="L26" t="n">
         <v>-0.3463999999999998</v>
@@ -2482,13 +2482,13 @@
         <v>6.524999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3501</v>
+        <v>5.8403</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3786000000000003</v>
+        <v>0.3786</v>
       </c>
       <c r="U26" t="n">
-        <v>3.9714</v>
+        <v>5.461700000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-5.1263</v>
